--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhilash Sharma\IdeaProjects\ATB5xLearnSelenium\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B007BA4-2CF0-45D5-BB0C-D0442AF8379A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CD345F-82A3-4C03-91AF-F6C7122BF4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -22,29 +22,29 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
+    <t>VAS1933@hyd</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>ExpectedResult</t>
+  </si>
+  <si>
+    <t>Invalid</t>
+  </si>
+  <si>
     <t>vemulaabhilash8433@gmail.com</t>
-  </si>
-  <si>
-    <t>VAS1933@hyd</t>
-  </si>
-  <si>
-    <t>Valid</t>
-  </si>
-  <si>
-    <t>vemulaabhilash03@gmail.com</t>
-  </si>
-  <si>
-    <t>Test@123</t>
-  </si>
-  <si>
-    <t>Invalid</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -55,6 +55,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -78,9 +85,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -300,33 +308,33 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhilash Sharma\IdeaProjects\ATB5xLearnSelenium\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CD345F-82A3-4C03-91AF-F6C7122BF4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2950E3-818D-4A60-8FCF-71BF15C117B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>VAS1933@hyd</t>
   </si>
@@ -38,6 +38,15 @@
   </si>
   <si>
     <t>vemulaabhilash8433@gmail.com</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
+    <t>vemulaabhilash03@gmail.com</t>
+  </si>
+  <si>
+    <t>VAS123@hyd</t>
   </si>
 </sst>
 </file>
@@ -307,7 +316,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.08984375" bestFit="1" customWidth="1"/>
@@ -326,15 +335,26 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
